--- a/data/trans_dic/P36BPD13_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,94; 91,99</t>
+          <t>80,43; 92,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,56; 90,85</t>
+          <t>80,27; 91,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,35; 90,35</t>
+          <t>82,88; 90,42</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,63; 86,02</t>
+          <t>75,62; 85,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,7; 94,61</t>
+          <t>87,74; 94,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,24; 89,96</t>
+          <t>83,41; 90,05</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,61; 88,31</t>
+          <t>81,92; 88,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,8; 88,11</t>
+          <t>83,04; 88,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,5; 87,55</t>
+          <t>83,65; 87,83</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,41; 95,54</t>
+          <t>84,14; 95,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,71; 90,35</t>
+          <t>85,64; 90,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,86; 93,01</t>
+          <t>85,91; 93,04</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,87; 83,53</t>
+          <t>76,92; 83,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,61; 89,84</t>
+          <t>85,4; 89,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,21; 86,21</t>
+          <t>82,05; 86,01</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79,87; 86,2</t>
+          <t>79,43; 86,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,66; 97,59</t>
+          <t>89,51; 97,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,2; 94,84</t>
+          <t>86,17; 94,31</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>85,36; 91,66</t>
+          <t>85,17; 91,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,49; 91,0</t>
+          <t>86,62; 91,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87,05; 90,64</t>
+          <t>86,61; 90,68</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,6; 88,51</t>
+          <t>83,39; 88,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,73; 90,99</t>
+          <t>87,72; 90,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,04; 89,2</t>
+          <t>86,06; 88,86</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas</t>
+          <t>Población que consumen preferentemente carne de pollo, pavo o conejo en vez de ternera, cerdo, hamburguesas o salchichas (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>323733; 367965</t>
+          <t>321706; 369614</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>249034; 280839</t>
+          <t>248129; 281876</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>583934; 640649</t>
+          <t>587692; 641183</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>319181; 363003</t>
+          <t>319121; 362181</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>442738; 477622</t>
+          <t>442921; 479024</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>771506; 833751</t>
+          <t>773107; 834646</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>435283; 471007</t>
+          <t>436954; 472230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>447089; 475799</t>
+          <t>448413; 476843</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>896261; 939702</t>
+          <t>897888; 942716</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>745475; 843794</t>
+          <t>743093; 844937</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>604962; 637708</t>
+          <t>604485; 637243</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1364307; 1477900</t>
+          <t>1365074; 1478491</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>427926; 464956</t>
+          <t>428202; 464848</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>467924; 491058</t>
+          <t>466801; 490295</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>906925; 951077</t>
+          <t>905266; 948917</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>290250; 313258</t>
+          <t>288647; 313583</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>543796; 591909</t>
+          <t>542888; 591801</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>836044; 919809</t>
+          <t>835731; 914759</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>240063; 257770</t>
+          <t>239511; 257809</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>365447; 384508</t>
+          <t>366014; 384843</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>612626; 637857</t>
+          <t>609492; 638174</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2875657; 3044662</t>
+          <t>2868463; 3037284</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3189337; 3307672</t>
+          <t>3188872; 3303712</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6087588; 6310817</t>
+          <t>6088937; 6286971</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36BPD13_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36BPD13_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80,43; 92,41</t>
+          <t>82,01; 92,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>80,27; 91,19</t>
+          <t>80,58; 91,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82,88; 90,42</t>
+          <t>83,26; 90,5</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,99%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,62; 85,82</t>
+          <t>77,05; 86,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87,74; 94,89</t>
+          <t>86,2; 92,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83,41; 90,05</t>
+          <t>82,98; 88,54</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,92; 88,54</t>
+          <t>82,86; 88,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>83,04; 88,31</t>
+          <t>82,75; 87,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,65; 87,83</t>
+          <t>83,76; 87,6</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,14; 95,67</t>
+          <t>82,41; 88,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,64; 90,28</t>
+          <t>85,14; 89,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>85,91; 93,04</t>
+          <t>84,59; 88,01</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,92; 83,51</t>
+          <t>77,33; 83,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>85,4; 89,7</t>
+          <t>85,1; 89,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82,05; 86,01</t>
+          <t>81,88; 85,78</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>79,43; 86,29</t>
+          <t>79,87; 86,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>89,51; 97,57</t>
+          <t>87,76; 92,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>86,17; 94,31</t>
+          <t>84,72; 88,51</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>85,17; 91,67</t>
+          <t>84,96; 91,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>86,62; 91,08</t>
+          <t>86,5; 91,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86,61; 90,68</t>
+          <t>86,63; 90,53</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>83,39; 88,3</t>
+          <t>83,14; 85,97</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,72; 90,88</t>
+          <t>86,82; 88,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>86,06; 88,86</t>
+          <t>85,35; 87,03</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>350624</t>
+          <t>357917</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>266304</t>
+          <t>310229</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>616928</t>
+          <t>668147</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>321706; 369614</t>
+          <t>334412; 375963</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>248129; 281876</t>
+          <t>288789; 326862</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>587692; 641183</t>
+          <t>637927; 693420</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>342131</t>
+          <t>389986</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>459897</t>
+          <t>442756</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>802028</t>
+          <t>832742</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>319121; 362181</t>
+          <t>366480; 411436</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>442921; 479024</t>
+          <t>426259; 456403</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>773107; 834646</t>
+          <t>805002; 858926</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>455530</t>
+          <t>531997</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>463729</t>
+          <t>528245</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>919259</t>
+          <t>1060242</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>436954; 472230</t>
+          <t>511792; 549392</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>448413; 476843</t>
+          <t>512213; 543912</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>897888; 942716</t>
+          <t>1035751; 1083319</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>788834</t>
+          <t>593282</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>621135</t>
+          <t>637428</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1409969</t>
+          <t>1230710</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>743093; 844937</t>
+          <t>573556; 612739</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>604485; 637243</t>
+          <t>620286; 650391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1365074; 1478491</t>
+          <t>1204939; 1253680</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>448235</t>
+          <t>487811</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>479638</t>
+          <t>529431</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>927874</t>
+          <t>1017243</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>428202; 464848</t>
+          <t>467496; 505879</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>466801; 490295</t>
+          <t>516532; 542498</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>905266; 948917</t>
+          <t>992082; 1039249</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>302116</t>
+          <t>334910</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>567102</t>
+          <t>393712</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>869218</t>
+          <t>728623</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>288647; 313583</t>
+          <t>321093; 348122</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>542888; 591801</t>
+          <t>383679; 403233</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>835731; 914759</t>
+          <t>711029; 742795</t>
         </is>
       </c>
     </row>
@@ -1498,17 +1498,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>249135</t>
+          <t>272472</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>375850</t>
+          <t>409898</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>624986</t>
+          <t>682370</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>239511; 257809</t>
+          <t>261527; 280843</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>366014; 384843</t>
+          <t>398369; 419291</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>609492; 638174</t>
+          <t>665660; 695610</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>2936605</t>
+          <t>2968376</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3233657</t>
+          <t>3251699</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6170262</t>
+          <t>6220076</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2868463; 3037284</t>
+          <t>2919385; 3018999</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3188872; 3303712</t>
+          <t>3216731; 3288283</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>6088937; 6286971</t>
+          <t>6159518; 6280462</t>
         </is>
       </c>
     </row>
